--- a/DesignData/Excel_Masters/EquipmentEnhanceData_Master.xlsx
+++ b/DesignData/Excel_Masters/EquipmentEnhanceData_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17910" windowHeight="10695"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentEnhanceData" sheetId="1" r:id="rId1"/>
@@ -19,33 +19,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>RequiredGold</t>
+    <t>MaxEnhanceLevel</t>
   </si>
   <si>
-    <t>RequiredMaterialCount</t>
+    <t>BaseGoldCost</t>
   </si>
   <si>
-    <t>StatMultiplier</t>
+    <t>GoldCostPerLevel</t>
   </si>
   <si>
-    <t>Common</t>
+    <t>StatBonusPerLevel</t>
   </si>
   <si>
-    <t>Uncommon</t>
+    <t>Cost_Common</t>
   </si>
   <si>
-    <t>Rare</t>
+    <t>Cost_Uncommon</t>
   </si>
   <si>
-    <t>Epic</t>
+    <t>Cost_Rare</t>
   </si>
   <si>
-    <t>Legendary</t>
+    <t>Cost_Epic</t>
+  </si>
+  <si>
+    <t>Cost_Legendary</t>
   </si>
 </sst>
 </file>
@@ -963,10 +966,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -979,75 +982,93 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
         <v>500</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
       <c r="D2">
-        <v>1.0249999999999999</v>
+        <v>200</v>
+      </c>
+      <c r="E2">
+        <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
         <v>1000</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
       <c r="D3">
-        <v>1.05</v>
+        <v>500</v>
+      </c>
+      <c r="E3">
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>2500</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D4">
-        <v>1.085</v>
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>5000</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D5">
-        <v>1.1499999999999999</v>
+        <v>3000</v>
+      </c>
+      <c r="E5">
+        <v>0.15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>15000</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="D6">
-        <v>1.2</v>
+        <v>10000</v>
+      </c>
+      <c r="E6">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
